--- a/public/templates/OBI_Test_Data_Template_WithTimer.xlsx
+++ b/public/templates/OBI_Test_Data_Template_WithTimer.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="With Timer" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,6 +398,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N64"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1152,40 +1168,40 @@
         <v>FFD (cm)</v>
       </c>
       <c r="B18" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
         <v>Tol Value</v>
       </c>
-      <c r="C18" t="str">
+      <c r="E18" t="str">
         <v>Header 1</v>
       </c>
-      <c r="D18" t="str">
+      <c r="F18" t="str">
         <v>Header 2</v>
       </c>
-      <c r="E18" t="str">
+      <c r="G18" t="str">
         <v>Header 3</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>kV</v>
       </c>
-      <c r="H18" t="str">
+      <c r="J18" t="str">
         <v>mAs</v>
       </c>
-      <c r="I18" t="str">
+      <c r="K18" t="str">
         <v>22</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
         <v>32</v>
       </c>
-      <c r="K18" t="str">
+      <c r="M18" t="str">
         <v>11</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1196,40 +1212,40 @@
         <v>100</v>
       </c>
       <c r="B19" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
         <v>0.05</v>
       </c>
-      <c r="C19" t="str">
+      <c r="E19" t="str">
         <v>22</v>
       </c>
-      <c r="D19" t="str">
+      <c r="F19" t="str">
         <v>32</v>
       </c>
-      <c r="E19" t="str">
+      <c r="G19" t="str">
         <v>11</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>60</v>
       </c>
-      <c r="H19" t="str">
+      <c r="J19" t="str">
         <v>10</v>
       </c>
-      <c r="I19" t="str">
+      <c r="K19" t="str">
         <v>1.2</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
         <v>1.3</v>
       </c>
-      <c r="K19" t="str">
+      <c r="M19" t="str">
         <v>1.25</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1255,25 +1271,25 @@
         <v/>
       </c>
       <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>80</v>
       </c>
-      <c r="H20" t="str">
+      <c r="J20" t="str">
         <v>20</v>
       </c>
-      <c r="I20" t="str">
+      <c r="K20" t="str">
         <v>2.5</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>2.6</v>
       </c>
-      <c r="K20" t="str">
+      <c r="M20" t="str">
         <v>2.55</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1994,13 +2010,13 @@
         <v>Time (sec)</v>
       </c>
       <c r="D37" t="str">
-        <v>Tolerance</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="E37" t="str">
+        <v>Tolerance Value</v>
+      </c>
+      <c r="F37" t="str">
         <v>Header 1</v>
-      </c>
-      <c r="F37" t="str">
-        <v/>
       </c>
       <c r="G37" t="str">
         <v>Header 2</v>
@@ -2009,16 +2025,16 @@
         <v>Header 3</v>
       </c>
       <c r="I37" t="str">
-        <v>mA</v>
+        <v>mA Applied</v>
       </c>
       <c r="J37" t="str">
-        <v>33</v>
+        <v>Meas 1</v>
       </c>
       <c r="K37" t="str">
-        <v>11</v>
+        <v>Meas 2</v>
       </c>
       <c r="L37" t="str">
-        <v>111</v>
+        <v>Meas 3</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -2038,19 +2054,19 @@
         <v>1</v>
       </c>
       <c r="D38" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="E38" t="str">
         <v>0.1</v>
       </c>
-      <c r="E38" t="str">
-        <v>33</v>
-      </c>
       <c r="F38" t="str">
-        <v/>
+        <v>Meas 1</v>
       </c>
       <c r="G38" t="str">
-        <v>11</v>
+        <v>Meas 2</v>
       </c>
       <c r="H38" t="str">
-        <v>111</v>
+        <v>Meas 3</v>
       </c>
       <c r="I38" t="str">
         <v>50</v>
